--- a/doc/COP-Berechnung.xlsx
+++ b/doc/COP-Berechnung.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Datum</t>
   </si>
@@ -32,23 +32,60 @@
     <t>kWh</t>
   </si>
   <si>
-    <t>MWh</t>
-  </si>
-  <si>
     <t>Wärmezähler</t>
   </si>
   <si>
     <t>Stromzähler</t>
+  </si>
+  <si>
+    <t>Diff Strom</t>
+  </si>
+  <si>
+    <t>Diff Wärme</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>Momentanwerte</t>
+  </si>
+  <si>
+    <t>Strom</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>Wärme</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>Gut</t>
+  </si>
+  <si>
+    <t>Rücklauf Temp.</t>
+  </si>
+  <si>
+    <t>ca. 35</t>
+  </si>
+  <si>
+    <t>Vorlauf Temp.</t>
+  </si>
+  <si>
+    <t>Schlecht</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,8 +100,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -77,8 +122,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -95,33 +146,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -402,47 +520,240 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="5"/>
-    <col min="2" max="2" width="27.85546875" style="9"/>
-    <col min="3" max="16384" width="27.85546875" style="6"/>
+    <col min="1" max="1" width="14.85546875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="25" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="27.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="24"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>45610</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="11">
         <v>158.6</v>
       </c>
-      <c r="C3" s="6">
+      <c r="D3" s="22">
         <v>9731</v>
       </c>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>45613</v>
+      </c>
+      <c r="B4" s="11">
+        <v>232.65</v>
+      </c>
+      <c r="C4" s="11">
+        <f>B4-B3</f>
+        <v>74.050000000000011</v>
+      </c>
+      <c r="D4" s="22">
+        <v>9977</v>
+      </c>
+      <c r="E4" s="11">
+        <f>D4-D3</f>
+        <v>246</v>
+      </c>
+      <c r="F4" s="25">
+        <f>E4/C4</f>
+        <v>3.3220796758946651</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D5" s="22"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D6" s="22"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D7" s="22"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D8" s="22"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D9" s="22"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D10" s="22"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D11" s="22"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="22"/>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="22"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D14" s="22"/>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D15" s="22"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D16" s="22"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D17" s="22"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D18" s="22"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="26"/>
+    </row>
+    <row r="20" spans="1:6" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="28"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="11">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="E22" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="F22" s="25">
+        <f>E22/D22</f>
+        <v>4.7346938775510203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="E24" s="11">
+        <v>9.6</v>
+      </c>
+      <c r="F24" s="25">
+        <f>E24/D24</f>
+        <v>2.8235294117647061</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;Z&amp;F&amp;R&amp;D</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/doc/COP-Berechnung.xlsx
+++ b/doc/COP-Berechnung.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Datum</t>
   </si>
@@ -75,6 +75,18 @@
   </si>
   <si>
     <t>Schlecht</t>
+  </si>
+  <si>
+    <t>42-48° Warmwaser</t>
+  </si>
+  <si>
+    <t>41-48° Vorlauf</t>
+  </si>
+  <si>
+    <t>33-40° Vorlauf</t>
+  </si>
+  <si>
+    <t>Zirkulation aus (27.11. - 11 Uhr)</t>
   </si>
 </sst>
 </file>
@@ -83,7 +95,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -94,7 +106,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,7 +114,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -174,72 +186,75 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -520,237 +535,315 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="27.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="27.85546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="25" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="27.85546875" style="3"/>
+    <col min="1" max="1" width="10.85546875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="29" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" style="15" customWidth="1"/>
+    <col min="8" max="8" width="35" style="15" customWidth="1"/>
+    <col min="9" max="16384" width="27.85546875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="24"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
         <v>45610</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="12">
         <v>158.6</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="13">
         <v>9731</v>
       </c>
-      <c r="E3" s="11"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="E3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
         <v>45613</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="12">
         <v>232.65</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="12">
         <f>B4-B3</f>
         <v>74.050000000000011</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="13">
         <v>9977</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="12">
         <f>D4-D3</f>
         <v>246</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="14">
         <f>E4/C4</f>
         <v>3.3220796758946651</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D5" s="22"/>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D6" s="22"/>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D7" s="22"/>
-      <c r="E7" s="11"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D8" s="22"/>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D9" s="22"/>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D10" s="22"/>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D11" s="22"/>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D12" s="22"/>
-      <c r="E12" s="11"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D13" s="22"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D14" s="22"/>
-      <c r="E14" s="11"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D15" s="22"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D16" s="22"/>
-      <c r="E16" s="11"/>
+      <c r="G4" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>45615</v>
+      </c>
+      <c r="B5" s="12">
+        <v>306.70999999999998</v>
+      </c>
+      <c r="C5" s="12">
+        <f>B5-B4</f>
+        <v>74.059999999999974</v>
+      </c>
+      <c r="D5" s="13">
+        <v>10233</v>
+      </c>
+      <c r="E5" s="12">
+        <f>D5-D4</f>
+        <v>256</v>
+      </c>
+      <c r="F5" s="14">
+        <f>E5/C5</f>
+        <v>3.4566567647853104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>45623</v>
+      </c>
+      <c r="B6" s="12">
+        <v>508.07</v>
+      </c>
+      <c r="C6" s="12">
+        <f>B6-B5</f>
+        <v>201.36</v>
+      </c>
+      <c r="D6" s="13">
+        <v>10950</v>
+      </c>
+      <c r="E6" s="12">
+        <f>D6-D5</f>
+        <v>717</v>
+      </c>
+      <c r="F6" s="14">
+        <f>E6/C6</f>
+        <v>3.5607866507747317</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="H7" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D8" s="13"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D9" s="13"/>
+      <c r="E9" s="12"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D10" s="13"/>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D11" s="13"/>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D13" s="13"/>
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D14" s="13"/>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D15" s="13"/>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D16" s="13"/>
+      <c r="E16" s="12"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D17" s="22"/>
-      <c r="E17" s="11"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D18" s="22"/>
-      <c r="E18" s="11"/>
-    </row>
-    <row r="19" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="D18" s="13"/>
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="26"/>
-    </row>
-    <row r="20" spans="1:6" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17" t="s">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+    </row>
+    <row r="20" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20" t="s">
+    <row r="21" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="28"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="12">
         <v>2.4500000000000002</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="12">
         <v>11.6</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="14">
         <f>E22/D22</f>
         <v>4.7346938775510203</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
+      <c r="D23" s="12">
+        <v>2.76</v>
+      </c>
+      <c r="E23" s="12">
+        <v>10.3</v>
+      </c>
+      <c r="F23" s="14">
+        <f>E23/D23</f>
+        <v>3.7318840579710151</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="B24" s="12">
+        <v>31.4</v>
+      </c>
+      <c r="D24" s="12">
+        <v>2.25</v>
+      </c>
+      <c r="E24" s="12">
+        <v>11.3</v>
+      </c>
+      <c r="F24" s="14">
+        <f>E24/D24</f>
+        <v>5.0222222222222221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D26" s="12">
         <v>3.4</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E26" s="12">
         <v>9.6</v>
       </c>
-      <c r="F24" s="25">
-        <f>E24/D24</f>
+      <c r="F26" s="14">
+        <f>E26/D26</f>
         <v>2.8235294117647061</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-    </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
     </row>
   </sheetData>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;Z&amp;F&amp;R&amp;D</oddFooter>

--- a/doc/COP-Berechnung.xlsx
+++ b/doc/COP-Berechnung.xlsx
@@ -672,8 +672,27 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
+      <c r="A7" s="11">
+        <v>45627</v>
+      </c>
+      <c r="B7" s="12">
+        <v>578.99</v>
+      </c>
+      <c r="C7" s="12">
+        <f>B7-B6</f>
+        <v>70.920000000000016</v>
+      </c>
+      <c r="D7" s="13">
+        <v>11245</v>
+      </c>
+      <c r="E7" s="12">
+        <f>D7-D6</f>
+        <v>295</v>
+      </c>
+      <c r="F7" s="14">
+        <f>E7/C7</f>
+        <v>4.1596164692611381</v>
+      </c>
       <c r="H7" s="15" t="s">
         <v>20</v>
       </c>
@@ -812,8 +831,16 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="D25" s="12">
+        <v>2.14</v>
+      </c>
+      <c r="E25" s="12">
+        <v>11.3</v>
+      </c>
+      <c r="F25" s="14">
+        <f>E25/D25</f>
+        <v>5.2803738317757007</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">

--- a/doc/COP-Berechnung.xlsx
+++ b/doc/COP-Berechnung.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="11505"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="11505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Wärmepumpe" sheetId="1" r:id="rId1"/>
+    <sheet name="Übersicht Dez. 2024" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>Datum</t>
   </si>
@@ -87,6 +88,24 @@
   </si>
   <si>
     <t>Zirkulation aus (27.11. - 11 Uhr)</t>
+  </si>
+  <si>
+    <t>27.11. - 10.12.2024</t>
+  </si>
+  <si>
+    <t>10.12. - 18.12.2024</t>
+  </si>
+  <si>
+    <t>Gesamtverbrauch am Stromzähler</t>
+  </si>
+  <si>
+    <t>Wärmepumpe</t>
+  </si>
+  <si>
+    <t>Wallbox</t>
+  </si>
+  <si>
+    <t>Hausverbrauch</t>
   </si>
 </sst>
 </file>
@@ -97,7 +116,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,8 +139,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,8 +167,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -182,37 +215,105 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -255,6 +356,57 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -538,336 +690,427 @@
   <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.85546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="29" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="35" style="15" customWidth="1"/>
-    <col min="9" max="16384" width="27.85546875" style="15"/>
+    <col min="1" max="1" width="16.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="35" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="27.85546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="37" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7" t="s">
+      <c r="G1" s="40"/>
+    </row>
+    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
+      <c r="D2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="38"/>
+      <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
+      <c r="A3" s="25">
         <v>45610</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="28">
         <v>158.6</v>
       </c>
-      <c r="D3" s="13">
+      <c r="C3" s="29"/>
+      <c r="D3" s="36">
         <v>9731</v>
       </c>
-      <c r="E3" s="12"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="42"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+      <c r="A4" s="25">
         <v>45613</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="28">
         <v>232.65</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="29">
         <f>B4-B3</f>
         <v>74.050000000000011</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="36">
         <v>9977</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="29">
         <f>D4-D3</f>
         <v>246</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="39">
         <f>E4/C4</f>
         <v>3.3220796758946651</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="42" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+      <c r="A5" s="25">
         <v>45615</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="28">
         <v>306.70999999999998</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="29">
         <f>B5-B4</f>
         <v>74.059999999999974</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="36">
         <v>10233</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="29">
         <f>D5-D4</f>
         <v>256</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="39">
         <f>E5/C5</f>
         <v>3.4566567647853104</v>
       </c>
+      <c r="G5" s="42"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
+      <c r="A6" s="25">
         <v>45623</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="28">
         <v>508.07</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="29">
         <f>B6-B5</f>
         <v>201.36</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="36">
         <v>10950</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="29">
         <f>D6-D5</f>
         <v>717</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="39">
         <f>E6/C6</f>
         <v>3.5607866507747317</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+      <c r="A7" s="25">
         <v>45627</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="28">
         <v>578.99</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="29">
         <f>B7-B6</f>
         <v>70.920000000000016</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="36">
         <v>11245</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="29">
         <f>D7-D6</f>
         <v>295</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="39">
         <f>E7/C7</f>
         <v>4.1596164692611381</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="G7" s="42"/>
+      <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
+      <c r="A8" s="25">
+        <v>45636</v>
+      </c>
+      <c r="B8" s="28">
+        <v>824</v>
+      </c>
+      <c r="C8" s="29">
+        <f>B8-B7</f>
+        <v>245.01</v>
+      </c>
+      <c r="D8" s="36">
+        <v>12144</v>
+      </c>
+      <c r="E8" s="29">
+        <f>D8-D7</f>
+        <v>899</v>
+      </c>
+      <c r="F8" s="39">
+        <f>E8/C8</f>
+        <v>3.6692379902861108</v>
+      </c>
+      <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
+      <c r="A9" s="25">
+        <v>45644</v>
+      </c>
+      <c r="B9" s="28">
+        <v>1020</v>
+      </c>
+      <c r="C9" s="29">
+        <f>B9-B8</f>
+        <v>196</v>
+      </c>
+      <c r="D9" s="36">
+        <v>12862</v>
+      </c>
+      <c r="E9" s="29">
+        <f>D9-D8</f>
+        <v>718</v>
+      </c>
+      <c r="F9" s="39">
+        <f>E9/C9</f>
+        <v>3.6632653061224492</v>
+      </c>
+      <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D12" s="13"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="42"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D13" s="13"/>
-      <c r="E13" s="12"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D14" s="13"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D15" s="13"/>
-      <c r="E15" s="12"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D16" s="13"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D18" s="13"/>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="42"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="25"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="42"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-    </row>
-    <row r="20" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25" t="s">
+    <row r="21" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="16"/>
+      <c r="B21" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="26"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="4">
         <v>2.4500000000000002</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="4">
         <v>11.6</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="6">
         <f>E22/D22</f>
         <v>4.7346938775510203</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D23" s="12">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="4">
         <v>2.76</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="4">
         <v>10.3</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="6">
         <f>E23/D23</f>
         <v>3.7318840579710151</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="12">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="4">
         <v>31.4</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="4">
         <v>2.25</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="4">
         <v>11.3</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="6">
         <f>E24/D24</f>
         <v>5.0222222222222221</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D25" s="12">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D25" s="4">
         <v>2.14</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="4">
         <v>11.3</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="6">
         <f>E25/D25</f>
         <v>5.2803738317757007</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="4">
         <v>3.4</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="4">
         <v>9.6</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="6">
         <f>E26/D26</f>
         <v>2.8235294117647061</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -876,4 +1119,72 @@
     <oddFooter>&amp;L&amp;Z&amp;F&amp;R&amp;D</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="22" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>1155</v>
+      </c>
+      <c r="C2">
+        <v>316</v>
+      </c>
+      <c r="D2">
+        <v>166</v>
+      </c>
+      <c r="E2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>341</v>
+      </c>
+      <c r="C3">
+        <v>196</v>
+      </c>
+      <c r="D3">
+        <v>94</v>
+      </c>
+      <c r="E3">
+        <f>B3-C3-D3</f>
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/COP-Berechnung.xlsx
+++ b/doc/COP-Berechnung.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Wärmepumpe" sheetId="1" state="visible" r:id="rId2"/>
@@ -597,7 +597,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="27.859375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="27.859375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="17.14"/>
@@ -610,7 +610,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="9" style="5" width="27.85"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="true" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="13" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -631,7 +631,7 @@
       </c>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" s="21" customFormat="true" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="21" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
         <v>6</v>
@@ -648,7 +648,7 @@
       <c r="F2" s="19"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="n">
         <v>45610</v>
       </c>
@@ -663,7 +663,7 @@
       <c r="F3" s="26"/>
       <c r="G3" s="27"/>
     </row>
-    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="n">
         <v>45613</v>
       </c>
@@ -689,7 +689,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="n">
         <v>45615</v>
       </c>
@@ -713,7 +713,7 @@
       </c>
       <c r="G5" s="27"/>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="n">
         <v>45623</v>
       </c>
@@ -742,7 +742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="n">
         <v>45627</v>
       </c>
@@ -769,7 +769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="n">
         <v>45636</v>
       </c>
@@ -916,16 +916,31 @@
       </c>
       <c r="G13" s="27"/>
     </row>
-    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="26"/>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>1710</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <f aca="false">B14-B13</f>
+        <v>394</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>15561</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <f aca="false">D14-D13</f>
+        <v>1534</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <f aca="false">E14/C14</f>
+        <v>3.89340101522843</v>
+      </c>
       <c r="G14" s="27"/>
     </row>
-    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="22"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -934,7 +949,7 @@
       <c r="F15" s="26"/>
       <c r="G15" s="27"/>
     </row>
-    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="22"/>
       <c r="B16" s="23"/>
       <c r="C16" s="24"/>
@@ -943,7 +958,7 @@
       <c r="F16" s="26"/>
       <c r="G16" s="27"/>
     </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="22"/>
       <c r="B17" s="23"/>
       <c r="C17" s="24"/>
@@ -952,11 +967,11 @@
       <c r="F17" s="26"/>
       <c r="G17" s="27"/>
     </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="28"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" s="32" customFormat="true" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="32" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
         <v>12</v>
       </c>
@@ -966,7 +981,7 @@
       <c r="E19" s="30"/>
       <c r="F19" s="31"/>
     </row>
-    <row r="20" s="36" customFormat="true" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="36" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33"/>
       <c r="B20" s="34" t="s">
         <v>13</v>
@@ -984,7 +999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" s="40" customFormat="true" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="40" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37"/>
       <c r="B21" s="38" t="s">
         <v>17</v>
@@ -1000,7 +1015,7 @@
       </c>
       <c r="F21" s="39"/>
     </row>
-    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1018,7 +1033,7 @@
         <v>4.73469387755102</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="2" t="n">
         <v>2.76</v>
       </c>
@@ -1030,7 +1045,7 @@
         <v>3.73188405797101</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="n">
         <v>31.4</v>
       </c>
@@ -1045,7 +1060,7 @@
         <v>5.02222222222222</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="2" t="n">
         <v>2.14</v>
       </c>
@@ -1057,15 +1072,23 @@
         <v>5.2803738317757</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <f aca="false">E26/D26</f>
+        <v>5.08620689655173</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
@@ -1093,11 +1116,11 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="0"/>
-      <c r="E30" s="0"/>
-      <c r="F30" s="0"/>
-    </row>
-    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
@@ -1296,7 +1319,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="n">
